--- a/スタッフマスター.xlsx
+++ b/スタッフマスター.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ローカルユーザー_PC-0000278\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C45CAC4-78F5-4B6E-96A4-B10B24BFA6FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF680DF1-5C75-4AE0-A0D7-4B3A905F98F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{6B59E9A4-843C-4428-B566-3D6F670A8F75}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="129">
   <si>
     <t>社員番号</t>
   </si>
@@ -425,28 +425,6 @@
     <t>オペレーター名</t>
   </si>
   <si>
-    <t>5月時給</t>
-    <rPh sb="1" eb="2">
-      <t>ガツ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジキュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>D0000448</t>
-  </si>
-  <si>
-    <t>鈴木紅美子0909</t>
-  </si>
-  <si>
-    <t>D0001181</t>
-  </si>
-  <si>
-    <t>鈴木翔太0113</t>
-  </si>
-  <si>
     <t>※月給</t>
     <rPh sb="1" eb="3">
       <t>ゲッキュウ</t>
@@ -460,11 +438,27 @@
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>時給</t>
+    <rPh sb="0" eb="2">
+      <t>ジキュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>D0001316</t>
+  </si>
+  <si>
+    <t>久保園大士0601</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="6" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -527,11 +521,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -552,9 +549,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -592,7 +589,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -698,7 +695,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -840,7 +837,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -848,7 +845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4F48F91-A699-4606-B7C8-455CAF2FFA06}">
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="10.75" bestFit="1" customWidth="1"/>
@@ -994,7 +991,7 @@
         <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1008,7 +1005,7 @@
         <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1022,7 +1019,7 @@
         <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1035,9 +1032,6 @@
       <c r="C13" t="s">
         <v>103</v>
       </c>
-      <c r="D13" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
@@ -1049,9 +1043,6 @@
       <c r="C14" t="s">
         <v>103</v>
       </c>
-      <c r="D14" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
@@ -1063,9 +1054,6 @@
       <c r="C15" t="s">
         <v>103</v>
       </c>
-      <c r="D15" t="s">
-        <v>35</v>
-      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
@@ -1189,9 +1177,6 @@
       <c r="C24" t="s">
         <v>102</v>
       </c>
-      <c r="D24" t="s">
-        <v>101</v>
-      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
@@ -1315,9 +1300,6 @@
       <c r="C33" t="s">
         <v>102</v>
       </c>
-      <c r="D33" t="s">
-        <v>101</v>
-      </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
@@ -1441,9 +1423,6 @@
       <c r="C42" t="s">
         <v>102</v>
       </c>
-      <c r="D42" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
@@ -1582,7 +1561,7 @@
         <v>120</v>
       </c>
       <c r="D52" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1595,9 +1574,6 @@
       <c r="C53" t="s">
         <v>120</v>
       </c>
-      <c r="D53" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
@@ -1610,7 +1586,7 @@
         <v>120</v>
       </c>
       <c r="D54" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1624,7 +1600,7 @@
         <v>120</v>
       </c>
       <c r="D55" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1635,9 +1611,23 @@
         <v>119</v>
       </c>
       <c r="C56" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D56" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" t="s">
+        <v>128</v>
+      </c>
+      <c r="C57" t="s">
+        <v>103</v>
+      </c>
+      <c r="D57" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1650,7 +1640,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F83CA3E6-F13B-429E-A12F-31144AA2831F}">
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="10.75" bestFit="1" customWidth="1"/>
@@ -1666,103 +1656,112 @@
         <v>123</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>300000</v>
+        <v>450000</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C3">
-        <v>380000</v>
+        <v>600000</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C4">
-        <v>2500</v>
+        <v>600000</v>
+      </c>
+      <c r="D4" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C5">
-        <v>1800</v>
+        <v>105</v>
+      </c>
+      <c r="C5" s="2">
+        <v>300000</v>
+      </c>
+      <c r="D5" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6">
-        <v>2500</v>
+        <v>41</v>
+      </c>
+      <c r="C6" s="2">
+        <v>380000</v>
+      </c>
+      <c r="D6" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C7">
-        <v>1300</v>
+        <v>51</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2500</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8">
+        <v>45</v>
+      </c>
+      <c r="C8" s="2">
         <v>2500</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9">
+        <v>49</v>
+      </c>
+      <c r="C9" s="2">
         <v>2500</v>
       </c>
     </row>
@@ -1773,8 +1772,8 @@
       <c r="B10" t="s">
         <v>83</v>
       </c>
-      <c r="C10">
-        <v>2200</v>
+      <c r="C10" s="2">
+        <v>2300</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1784,8 +1783,8 @@
       <c r="B11" t="s">
         <v>79</v>
       </c>
-      <c r="C11">
-        <v>2000</v>
+      <c r="C11" s="2">
+        <v>2100</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1795,8 +1794,8 @@
       <c r="B12" t="s">
         <v>81</v>
       </c>
-      <c r="C12">
-        <v>2300</v>
+      <c r="C12" s="2">
+        <v>2400</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -1806,7 +1805,7 @@
       <c r="B13" t="s">
         <v>91</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>1300</v>
       </c>
     </row>
@@ -1817,7 +1816,7 @@
       <c r="B14" t="s">
         <v>43</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2">
         <v>2500</v>
       </c>
     </row>
@@ -1828,7 +1827,7 @@
       <c r="B15" t="s">
         <v>67</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2">
         <v>2500</v>
       </c>
     </row>
@@ -1839,7 +1838,7 @@
       <c r="B16" t="s">
         <v>47</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="2">
         <v>2500</v>
       </c>
     </row>
@@ -1850,7 +1849,7 @@
       <c r="B17" t="s">
         <v>69</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="2">
         <v>2400</v>
       </c>
     </row>
@@ -1861,8 +1860,8 @@
       <c r="B18" t="s">
         <v>77</v>
       </c>
-      <c r="C18">
-        <v>2100</v>
+      <c r="C18" s="2">
+        <v>2200</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -1872,7 +1871,7 @@
       <c r="B19" t="s">
         <v>73</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="2">
         <v>2500</v>
       </c>
     </row>
@@ -1883,7 +1882,7 @@
       <c r="B20" t="s">
         <v>63</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="2">
         <v>2500</v>
       </c>
     </row>
@@ -1894,7 +1893,7 @@
       <c r="B21" t="s">
         <v>61</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="2">
         <v>2500</v>
       </c>
     </row>
@@ -1905,402 +1904,294 @@
       <c r="B22" t="s">
         <v>57</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="2">
         <v>2500</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23">
+        <v>59</v>
+      </c>
+      <c r="C23" s="2">
         <v>2500</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24">
+        <v>65</v>
+      </c>
+      <c r="C24" s="2">
         <v>2500</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
-      </c>
-      <c r="C25">
+        <v>55</v>
+      </c>
+      <c r="C25" s="2">
         <v>2500</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26">
-        <v>2500</v>
+        <v>107</v>
+      </c>
+      <c r="C26" s="2">
+        <v>2200</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
-        <v>107</v>
-      </c>
-      <c r="C27">
-        <v>2100</v>
+        <v>95</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1900</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
-      </c>
-      <c r="C28">
-        <v>1800</v>
+        <v>87</v>
+      </c>
+      <c r="C28" s="2">
+        <v>2500</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29">
+        <v>85</v>
+      </c>
+      <c r="C29" s="2">
         <v>2400</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
-      </c>
-      <c r="C30">
-        <v>2300</v>
+        <v>97</v>
+      </c>
+      <c r="C30" s="2">
+        <v>1900</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
-      </c>
-      <c r="C31">
-        <v>2000</v>
+        <v>93</v>
+      </c>
+      <c r="C31" s="2">
+        <v>2100</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32">
-        <v>2200</v>
+        <v>75</v>
+      </c>
+      <c r="C32" s="2">
+        <v>2500</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
-      </c>
-      <c r="C33">
-        <v>2500</v>
+        <v>99</v>
+      </c>
+      <c r="C33" s="2">
+        <v>2000</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="B34" t="s">
-        <v>128</v>
-      </c>
-      <c r="C34">
-        <v>1900</v>
+        <v>119</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1800</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>98</v>
+        <v>5</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35">
-        <v>2000</v>
+        <v>6</v>
+      </c>
+      <c r="C35" s="2">
+        <v>2100</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="B36" t="s">
-        <v>119</v>
-      </c>
-      <c r="C36">
-        <v>1800</v>
+        <v>20</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1400</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37">
-        <v>2100</v>
+        <v>10</v>
+      </c>
+      <c r="C37" s="2">
+        <v>2000</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38">
-        <v>1300</v>
+        <v>12</v>
+      </c>
+      <c r="C38" s="2">
+        <v>2100</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>114</v>
       </c>
       <c r="B39" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39">
-        <v>2000</v>
+        <v>115</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1400</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>113</v>
-      </c>
-      <c r="C40">
+        <v>22</v>
+      </c>
+      <c r="C40" s="2">
         <v>1300</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
-      </c>
-      <c r="C41">
-        <v>2100</v>
+        <v>8</v>
+      </c>
+      <c r="C41" s="2">
+        <v>1400</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>115</v>
-      </c>
-      <c r="C42">
-        <v>1400</v>
+        <v>24</v>
+      </c>
+      <c r="C42" s="2">
+        <v>1300</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B43" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43">
+        <v>14</v>
+      </c>
+      <c r="C43" s="2">
         <v>1300</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B44" t="s">
-        <v>8</v>
-      </c>
-      <c r="C44">
-        <v>1500</v>
+        <v>16</v>
+      </c>
+      <c r="C44" s="2">
+        <v>1400</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45">
-        <v>1400</v>
+        <v>18</v>
+      </c>
+      <c r="C45" s="2">
+        <v>1600</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
-      </c>
-      <c r="C46">
-        <v>1400</v>
+        <v>111</v>
+      </c>
+      <c r="C46" s="2">
+        <v>1500</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>116</v>
       </c>
       <c r="B47" t="s">
-        <v>14</v>
-      </c>
-      <c r="C47">
-        <v>1300</v>
+        <v>117</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1500</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" t="s">
-        <v>17</v>
-      </c>
-      <c r="B49" t="s">
-        <v>18</v>
-      </c>
-      <c r="C49">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" t="s">
-        <v>110</v>
-      </c>
-      <c r="B50" t="s">
-        <v>111</v>
-      </c>
-      <c r="C50">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" t="s">
-        <v>116</v>
-      </c>
-      <c r="B51" t="s">
-        <v>117</v>
-      </c>
-      <c r="C51">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" t="s">
-        <v>27</v>
-      </c>
-      <c r="B52" t="s">
-        <v>28</v>
-      </c>
-      <c r="C52">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" t="s">
-        <v>29</v>
-      </c>
-      <c r="B53" t="s">
-        <v>30</v>
-      </c>
-      <c r="C53">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" t="s">
-        <v>108</v>
-      </c>
-      <c r="B54" t="s">
         <v>109</v>
       </c>
-      <c r="C54">
+      <c r="C48" s="2">
         <v>2100</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" t="s">
-        <v>3</v>
-      </c>
-      <c r="B55" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55">
-        <v>450000</v>
-      </c>
-      <c r="D55" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" t="s">
-        <v>36</v>
-      </c>
-      <c r="B56" t="s">
-        <v>37</v>
-      </c>
-      <c r="C56">
-        <v>600000</v>
-      </c>
-      <c r="D56" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" t="s">
-        <v>39</v>
-      </c>
-      <c r="C57">
-        <v>600000</v>
-      </c>
-      <c r="D57" t="s">
-        <v>129</v>
       </c>
     </row>
   </sheetData>
